--- a/PawPewPewTranslate (1).xlsx
+++ b/PawPewPewTranslate (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project Website\PawPewPew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56583348-7066-4B17-9D4B-F11D063969F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC1D8E1-F81F-4B69-AE60-3384347E48DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{15B7F092-291F-47B8-BF64-7EB67EA1D344}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{15B7F092-291F-47B8-BF64-7EB67EA1D344}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -1037,7 +1037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1072,7 +1072,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2709,7 +2708,7 @@
       <c r="F3" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="4" t="s">
         <v>249</v>
       </c>
     </row>
@@ -2732,7 +2731,7 @@
       <c r="F4" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="4" t="s">
         <v>270</v>
       </c>
     </row>
@@ -2755,7 +2754,7 @@
       <c r="F5" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="4" t="s">
         <v>255</v>
       </c>
     </row>
